--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/100000/Output_22_44.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/100000/Output_22_44.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2306332.694774906</v>
+        <v>2300652.506489728</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5413711.842050616</v>
+        <v>5413711.842050619</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11405092.40681099</v>
+        <v>11402720.39333456</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5385203.386182076</v>
+        <v>5385335.150942775</v>
       </c>
     </row>
     <row r="11">
@@ -8600,7 +8600,7 @@
         <v>138.9257839476051</v>
       </c>
       <c r="N10" t="n">
-        <v>127.6855444652244</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O10" t="n">
         <v>138.4565384518428</v>
@@ -9226,19 +9226,19 @@
         <v>137.841438974359</v>
       </c>
       <c r="L18" t="n">
-        <v>138.5543797798746</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M18" t="n">
-        <v>142.1340339220187</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N18" t="n">
-        <v>131.3417120833336</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O18" t="n">
-        <v>142.5962444444448</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P18" t="n">
-        <v>133.9744074143306</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q18" t="n">
         <v>139.9817740860215</v>
@@ -9463,16 +9463,16 @@
         <v>137.841438974359</v>
       </c>
       <c r="L21" t="n">
-        <v>138.5543797798744</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M21" t="n">
-        <v>142.1340339220185</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N21" t="n">
-        <v>131.3417120833335</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O21" t="n">
-        <v>142.5962444444446</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P21" t="n">
         <v>133.9744074143302</v>
@@ -9700,16 +9700,16 @@
         <v>137.841438974359</v>
       </c>
       <c r="L24" t="n">
-        <v>138.5543797798746</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M24" t="n">
-        <v>142.1340339220187</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N24" t="n">
-        <v>131.3417120833337</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O24" t="n">
-        <v>142.5962444444448</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P24" t="n">
         <v>133.9744074143302</v>
@@ -9861,7 +9861,7 @@
         <v>235.7664149699872</v>
       </c>
       <c r="M26" t="n">
-        <v>230.3462332272723</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N26" t="n">
         <v>229.4130635965909</v>
@@ -9937,16 +9937,16 @@
         <v>137.841438974359</v>
       </c>
       <c r="L27" t="n">
-        <v>138.5543797798746</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M27" t="n">
-        <v>142.1340339220188</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N27" t="n">
-        <v>131.3417120833338</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O27" t="n">
-        <v>142.5962444444448</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P27" t="n">
         <v>133.9744074143302</v>
@@ -10174,16 +10174,16 @@
         <v>137.841438974359</v>
       </c>
       <c r="L30" t="n">
-        <v>138.5543797798747</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M30" t="n">
-        <v>142.1340339220189</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N30" t="n">
-        <v>131.3417120833338</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O30" t="n">
-        <v>142.5962444444449</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P30" t="n">
         <v>133.9744074143302</v>
@@ -10411,16 +10411,16 @@
         <v>137.841438974359</v>
       </c>
       <c r="L33" t="n">
-        <v>138.5543797798747</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M33" t="n">
-        <v>142.1340339220188</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N33" t="n">
-        <v>131.3417120833336</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O33" t="n">
-        <v>142.596244444445</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P33" t="n">
         <v>133.9744074143302</v>
@@ -10648,16 +10648,16 @@
         <v>137.841438974359</v>
       </c>
       <c r="L36" t="n">
-        <v>138.5543797798748</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M36" t="n">
-        <v>142.1340339220189</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N36" t="n">
-        <v>131.3417120833336</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O36" t="n">
-        <v>142.5962444444449</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P36" t="n">
         <v>133.9744074143302</v>
@@ -10885,19 +10885,19 @@
         <v>137.841438974359</v>
       </c>
       <c r="L39" t="n">
-        <v>138.5543797798745</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M39" t="n">
-        <v>142.1340339220189</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N39" t="n">
-        <v>131.3417120833336</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O39" t="n">
-        <v>142.5962444444449</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P39" t="n">
-        <v>133.9744074143305</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q39" t="n">
         <v>139.9817740860215</v>
@@ -11122,19 +11122,19 @@
         <v>137.841438974359</v>
       </c>
       <c r="L42" t="n">
-        <v>138.5543797798745</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M42" t="n">
-        <v>142.1340339220187</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N42" t="n">
-        <v>131.3417120833336</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O42" t="n">
-        <v>142.5962444444447</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P42" t="n">
-        <v>133.9744074143305</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q42" t="n">
         <v>139.9817740860215</v>
@@ -11438,16 +11438,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L46" t="n">
-        <v>134.8846762812385</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M46" t="n">
-        <v>138.9257839476052</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N46" t="n">
         <v>127.6855444652332</v>
       </c>
       <c r="O46" t="n">
-        <v>138.456538451843</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P46" t="n">
         <v>135.0065633140411</v>
@@ -22516,10 +22516,10 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>6.876045741711209</v>
+        <v>6.876045741711437</v>
       </c>
       <c r="G2" t="n">
-        <v>15.30273751513482</v>
+        <v>15.30273751513505</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -22707,7 +22707,7 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>8.640199666842818e-12</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -22753,10 +22753,10 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>6.876045741711323</v>
+        <v>6.876045741711437</v>
       </c>
       <c r="G5" t="n">
-        <v>15.30273751513494</v>
+        <v>15.30273751513505</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -22917,7 +22917,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>8.640199666842818e-12</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -22990,10 +22990,10 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>6.876045741711323</v>
+        <v>6.876045741711437</v>
       </c>
       <c r="G8" t="n">
-        <v>15.30273751513494</v>
+        <v>15.30273751513505</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -23172,7 +23172,7 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>8.819342562646577e-12</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -23215,28 +23215,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>347.7338416634806</v>
+        <v>344.2036505416006</v>
       </c>
       <c r="C11" t="n">
-        <v>330.2728917710076</v>
+        <v>326.7427006491275</v>
       </c>
       <c r="D11" t="n">
-        <v>319.683041620683</v>
+        <v>316.1528504988029</v>
       </c>
       <c r="E11" t="n">
-        <v>346.9303700722618</v>
+        <v>343.4001789503818</v>
       </c>
       <c r="F11" t="n">
-        <v>371.8760457417114</v>
+        <v>368.3458546198314</v>
       </c>
       <c r="G11" t="n">
-        <v>380.302737515135</v>
+        <v>376.772546393255</v>
       </c>
       <c r="H11" t="n">
-        <v>304.4748021157671</v>
+        <v>300.9446109938871</v>
       </c>
       <c r="I11" t="n">
-        <v>175.4758895704059</v>
+        <v>171.9456984485259</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -23263,28 +23263,28 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>114.8691179411497</v>
+        <v>111.3389268192697</v>
       </c>
       <c r="S11" t="n">
-        <v>174.0200695862453</v>
+        <v>170.4898784643653</v>
       </c>
       <c r="T11" t="n">
-        <v>188.0958495641314</v>
+        <v>184.5656584422513</v>
       </c>
       <c r="U11" t="n">
-        <v>216.3456529078365</v>
+        <v>212.8154617859565</v>
       </c>
       <c r="V11" t="n">
-        <v>292.7522584701349</v>
+        <v>289.2220673482549</v>
       </c>
       <c r="W11" t="n">
-        <v>314.240968717413</v>
+        <v>310.710777595533</v>
       </c>
       <c r="X11" t="n">
-        <v>334.731100678469</v>
+        <v>331.200909556589</v>
       </c>
       <c r="Y11" t="n">
-        <v>351.2379386560536</v>
+        <v>347.7077475341736</v>
       </c>
     </row>
     <row r="12">
@@ -23294,28 +23294,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>131.5331836498673</v>
+        <v>128.0029925279873</v>
       </c>
       <c r="C12" t="n">
-        <v>137.7084989883157</v>
+        <v>134.1783078664357</v>
       </c>
       <c r="D12" t="n">
-        <v>112.4450655646388</v>
+        <v>108.9148744427587</v>
       </c>
       <c r="E12" t="n">
-        <v>122.6450804554009</v>
+        <v>119.1148893335209</v>
       </c>
       <c r="F12" t="n">
-        <v>110.0692123933839</v>
+        <v>106.5390212715039</v>
       </c>
       <c r="G12" t="n">
-        <v>102.3435171632106</v>
+        <v>98.81332604133061</v>
       </c>
       <c r="H12" t="n">
-        <v>77.23544423649646</v>
+        <v>73.70525311461644</v>
       </c>
       <c r="I12" t="n">
-        <v>54.39663285141507</v>
+        <v>50.86644172953505</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -23342,28 +23342,28 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>65.15783415264313</v>
+        <v>61.62764303076311</v>
       </c>
       <c r="S12" t="n">
-        <v>136.6831711038378</v>
+        <v>133.1529799819578</v>
       </c>
       <c r="T12" t="n">
-        <v>165.1647286948216</v>
+        <v>161.6345375729416</v>
       </c>
       <c r="U12" t="n">
-        <v>190.9413820809748</v>
+        <v>187.4111909590948</v>
       </c>
       <c r="V12" t="n">
-        <v>197.8005871494253</v>
+        <v>194.2703960275452</v>
       </c>
       <c r="W12" t="n">
-        <v>216.6949831609196</v>
+        <v>213.1647920390396</v>
       </c>
       <c r="X12" t="n">
-        <v>170.7729852034775</v>
+        <v>167.2427940815975</v>
       </c>
       <c r="Y12" t="n">
-        <v>170.6826957773044</v>
+        <v>167.1525046554243</v>
       </c>
     </row>
     <row r="13">
@@ -23373,31 +23373,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>144.8319801819373</v>
+        <v>141.3017890600573</v>
       </c>
       <c r="C13" t="n">
-        <v>132.2468210986278</v>
+        <v>128.7166299767478</v>
       </c>
       <c r="D13" t="n">
-        <v>113.6154730182124</v>
+        <v>110.0852818963323</v>
       </c>
       <c r="E13" t="n">
-        <v>111.4339626465692</v>
+        <v>107.9037715246891</v>
       </c>
       <c r="F13" t="n">
-        <v>110.4210480229312</v>
+        <v>106.8908569010512</v>
       </c>
       <c r="G13" t="n">
-        <v>132.9909793584588</v>
+        <v>129.4607882365787</v>
       </c>
       <c r="H13" t="n">
-        <v>127.2271725074396</v>
+        <v>123.6969813855596</v>
       </c>
       <c r="I13" t="n">
-        <v>120.4504749272583</v>
+        <v>116.9202838053783</v>
       </c>
       <c r="J13" t="n">
-        <v>58.35918011667278</v>
+        <v>54.82898899479275</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -23418,31 +23418,31 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>51.16204325169439</v>
+        <v>47.63185212981436</v>
       </c>
       <c r="R13" t="n">
-        <v>142.2933913771695</v>
+        <v>138.7632002552895</v>
       </c>
       <c r="S13" t="n">
-        <v>189.0165980369723</v>
+        <v>185.4864069150922</v>
       </c>
       <c r="T13" t="n">
-        <v>192.9455894282815</v>
+        <v>189.4153983064015</v>
       </c>
       <c r="U13" t="n">
-        <v>251.3190293564909</v>
+        <v>247.7888382346109</v>
       </c>
       <c r="V13" t="n">
-        <v>217.137643323828</v>
+        <v>213.607452201948</v>
       </c>
       <c r="W13" t="n">
-        <v>251.522998336591</v>
+        <v>247.992807214711</v>
       </c>
       <c r="X13" t="n">
-        <v>190.7096553890372</v>
+        <v>187.1794642671571</v>
       </c>
       <c r="Y13" t="n">
-        <v>183.5846533520948</v>
+        <v>180.0544622302148</v>
       </c>
     </row>
     <row r="14">
@@ -23452,28 +23452,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>288.7338416634822</v>
+        <v>289.3746615468078</v>
       </c>
       <c r="C14" t="n">
-        <v>271.2728917710076</v>
+        <v>271.9137116543347</v>
       </c>
       <c r="D14" t="n">
-        <v>260.683041620683</v>
+        <v>261.3238615040102</v>
       </c>
       <c r="E14" t="n">
-        <v>287.9303700722618</v>
+        <v>288.571189955589</v>
       </c>
       <c r="F14" t="n">
-        <v>312.8760457417114</v>
+        <v>313.5168656250387</v>
       </c>
       <c r="G14" t="n">
-        <v>321.302737515135</v>
+        <v>321.9435573984623</v>
       </c>
       <c r="H14" t="n">
-        <v>245.4748021157671</v>
+        <v>246.1156219990944</v>
       </c>
       <c r="I14" t="n">
-        <v>116.4758895704059</v>
+        <v>117.1167094537331</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -23500,28 +23500,28 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>55.8691179411497</v>
+        <v>56.50993782447691</v>
       </c>
       <c r="S14" t="n">
-        <v>115.0200695862453</v>
+        <v>115.6608894695726</v>
       </c>
       <c r="T14" t="n">
-        <v>129.0958495641314</v>
+        <v>129.7366694474586</v>
       </c>
       <c r="U14" t="n">
-        <v>157.3456529078365</v>
+        <v>157.9864727911637</v>
       </c>
       <c r="V14" t="n">
-        <v>233.7522584701349</v>
+        <v>234.3930783534621</v>
       </c>
       <c r="W14" t="n">
-        <v>255.240968717413</v>
+        <v>255.8817886007402</v>
       </c>
       <c r="X14" t="n">
-        <v>275.731100678469</v>
+        <v>276.3719205617963</v>
       </c>
       <c r="Y14" t="n">
-        <v>292.2379386560536</v>
+        <v>292.8787585393808</v>
       </c>
     </row>
     <row r="15">
@@ -23531,25 +23531,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>72.53318364986734</v>
+        <v>73.17400353319456</v>
       </c>
       <c r="C15" t="n">
-        <v>78.70849898831574</v>
+        <v>79.34931887164296</v>
       </c>
       <c r="D15" t="n">
-        <v>53.44506556463875</v>
+        <v>54.08588544796598</v>
       </c>
       <c r="E15" t="n">
-        <v>63.64508045540094</v>
+        <v>64.28590033872817</v>
       </c>
       <c r="F15" t="n">
-        <v>51.06921239338388</v>
+        <v>51.7100322767111</v>
       </c>
       <c r="G15" t="n">
-        <v>43.34351716321063</v>
+        <v>43.98433704653786</v>
       </c>
       <c r="H15" t="n">
-        <v>18.23544423649646</v>
+        <v>18.87626411982369</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -23579,28 +23579,28 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>6.157834152643133</v>
+        <v>6.798654035970358</v>
       </c>
       <c r="S15" t="n">
-        <v>77.68317110383782</v>
+        <v>78.32399098716505</v>
       </c>
       <c r="T15" t="n">
-        <v>106.1647286948216</v>
+        <v>106.8055485781488</v>
       </c>
       <c r="U15" t="n">
-        <v>131.9413820809748</v>
+        <v>132.582201964302</v>
       </c>
       <c r="V15" t="n">
-        <v>138.8005871494253</v>
+        <v>139.4414070327525</v>
       </c>
       <c r="W15" t="n">
-        <v>157.6949831609196</v>
+        <v>158.3358030442468</v>
       </c>
       <c r="X15" t="n">
-        <v>111.7729852034775</v>
+        <v>112.4138050868047</v>
       </c>
       <c r="Y15" t="n">
-        <v>111.6826957773044</v>
+        <v>112.3235156606316</v>
       </c>
     </row>
     <row r="16">
@@ -23610,28 +23610,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>85.8319801819373</v>
+        <v>86.47280006526452</v>
       </c>
       <c r="C16" t="n">
-        <v>73.24682109862783</v>
+        <v>73.88764098195506</v>
       </c>
       <c r="D16" t="n">
-        <v>54.61547301821236</v>
+        <v>55.25629290153958</v>
       </c>
       <c r="E16" t="n">
-        <v>52.43396264656917</v>
+        <v>53.0747825298964</v>
       </c>
       <c r="F16" t="n">
-        <v>51.42104802293125</v>
+        <v>52.06186790625847</v>
       </c>
       <c r="G16" t="n">
-        <v>73.99097935845876</v>
+        <v>74.63179924178598</v>
       </c>
       <c r="H16" t="n">
-        <v>68.22717250743958</v>
+        <v>68.8679923907668</v>
       </c>
       <c r="I16" t="n">
-        <v>61.45047492725828</v>
+        <v>62.09129481058551</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -23658,28 +23658,28 @@
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>83.29339137716948</v>
+        <v>83.93421126049671</v>
       </c>
       <c r="S16" t="n">
-        <v>130.0165980369723</v>
+        <v>130.6574179202995</v>
       </c>
       <c r="T16" t="n">
-        <v>133.9455894282815</v>
+        <v>134.5864093116087</v>
       </c>
       <c r="U16" t="n">
-        <v>192.3190293564909</v>
+        <v>192.9598492398181</v>
       </c>
       <c r="V16" t="n">
-        <v>158.137643323828</v>
+        <v>158.7784632071552</v>
       </c>
       <c r="W16" t="n">
-        <v>192.522998336591</v>
+        <v>193.1638182199182</v>
       </c>
       <c r="X16" t="n">
-        <v>131.7096553890372</v>
+        <v>132.3504752723644</v>
       </c>
       <c r="Y16" t="n">
-        <v>124.5846533520948</v>
+        <v>125.225473235422</v>
       </c>
     </row>
     <row r="17">
@@ -23689,28 +23689,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>288.7338416634827</v>
+        <v>289.3746615468078</v>
       </c>
       <c r="C17" t="n">
-        <v>271.2728917710076</v>
+        <v>271.9137116543347</v>
       </c>
       <c r="D17" t="n">
-        <v>260.683041620683</v>
+        <v>261.3238615040102</v>
       </c>
       <c r="E17" t="n">
-        <v>287.9303700722618</v>
+        <v>288.571189955589</v>
       </c>
       <c r="F17" t="n">
-        <v>312.8760457417114</v>
+        <v>313.5168656250387</v>
       </c>
       <c r="G17" t="n">
-        <v>321.302737515135</v>
+        <v>321.9435573984623</v>
       </c>
       <c r="H17" t="n">
-        <v>245.4748021157671</v>
+        <v>246.1156219990944</v>
       </c>
       <c r="I17" t="n">
-        <v>116.4758895704059</v>
+        <v>117.1167094537331</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -23737,28 +23737,28 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>55.8691179411497</v>
+        <v>56.50993782447691</v>
       </c>
       <c r="S17" t="n">
-        <v>115.0200695862453</v>
+        <v>115.6608894695726</v>
       </c>
       <c r="T17" t="n">
-        <v>129.0958495641314</v>
+        <v>129.7366694474586</v>
       </c>
       <c r="U17" t="n">
-        <v>157.3456529078365</v>
+        <v>157.9864727911637</v>
       </c>
       <c r="V17" t="n">
-        <v>233.7522584701349</v>
+        <v>234.3930783534621</v>
       </c>
       <c r="W17" t="n">
-        <v>255.240968717413</v>
+        <v>255.8817886007402</v>
       </c>
       <c r="X17" t="n">
-        <v>275.731100678469</v>
+        <v>276.3719205617963</v>
       </c>
       <c r="Y17" t="n">
-        <v>292.2379386560536</v>
+        <v>292.8787585393808</v>
       </c>
     </row>
     <row r="18">
@@ -23768,25 +23768,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>72.53318364986734</v>
+        <v>73.17400353319456</v>
       </c>
       <c r="C18" t="n">
-        <v>78.70849898831574</v>
+        <v>79.34931887164296</v>
       </c>
       <c r="D18" t="n">
-        <v>53.44506556463875</v>
+        <v>54.08588544796598</v>
       </c>
       <c r="E18" t="n">
-        <v>63.64508045540094</v>
+        <v>64.28590033872817</v>
       </c>
       <c r="F18" t="n">
-        <v>51.06921239338388</v>
+        <v>51.7100322767111</v>
       </c>
       <c r="G18" t="n">
-        <v>43.34351716321063</v>
+        <v>43.98433704653786</v>
       </c>
       <c r="H18" t="n">
-        <v>18.23544423649646</v>
+        <v>18.87626411982369</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -23816,28 +23816,28 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>6.157834152643133</v>
+        <v>6.798654035970358</v>
       </c>
       <c r="S18" t="n">
-        <v>77.68317110383782</v>
+        <v>78.32399098716505</v>
       </c>
       <c r="T18" t="n">
-        <v>106.1647286948216</v>
+        <v>106.8055485781488</v>
       </c>
       <c r="U18" t="n">
-        <v>131.9413820809748</v>
+        <v>132.582201964302</v>
       </c>
       <c r="V18" t="n">
-        <v>138.8005871494253</v>
+        <v>139.4414070327525</v>
       </c>
       <c r="W18" t="n">
-        <v>157.6949831609196</v>
+        <v>158.3358030442468</v>
       </c>
       <c r="X18" t="n">
-        <v>111.7729852034775</v>
+        <v>112.4138050868047</v>
       </c>
       <c r="Y18" t="n">
-        <v>111.6826957773044</v>
+        <v>112.3235156606316</v>
       </c>
     </row>
     <row r="19">
@@ -23847,28 +23847,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>85.8319801819373</v>
+        <v>86.47280006526452</v>
       </c>
       <c r="C19" t="n">
-        <v>73.24682109862783</v>
+        <v>73.88764098195506</v>
       </c>
       <c r="D19" t="n">
-        <v>54.61547301821236</v>
+        <v>55.25629290153958</v>
       </c>
       <c r="E19" t="n">
-        <v>52.43396264656917</v>
+        <v>53.0747825298964</v>
       </c>
       <c r="F19" t="n">
-        <v>51.42104802293125</v>
+        <v>52.06186790625847</v>
       </c>
       <c r="G19" t="n">
-        <v>73.99097935845876</v>
+        <v>74.63179924178598</v>
       </c>
       <c r="H19" t="n">
-        <v>68.22717250743958</v>
+        <v>68.8679923907668</v>
       </c>
       <c r="I19" t="n">
-        <v>61.45047492725828</v>
+        <v>62.09129481058551</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -23895,28 +23895,28 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>83.29339137716948</v>
+        <v>83.93421126049671</v>
       </c>
       <c r="S19" t="n">
-        <v>130.0165980369723</v>
+        <v>130.6574179202995</v>
       </c>
       <c r="T19" t="n">
-        <v>133.9455894282815</v>
+        <v>134.5864093116087</v>
       </c>
       <c r="U19" t="n">
-        <v>192.3190293564909</v>
+        <v>192.9598492398181</v>
       </c>
       <c r="V19" t="n">
-        <v>158.137643323828</v>
+        <v>158.7784632071552</v>
       </c>
       <c r="W19" t="n">
-        <v>192.522998336591</v>
+        <v>193.1638182199182</v>
       </c>
       <c r="X19" t="n">
-        <v>131.7096553890372</v>
+        <v>132.3504752723644</v>
       </c>
       <c r="Y19" t="n">
-        <v>124.5846533520948</v>
+        <v>125.225473235422</v>
       </c>
     </row>
     <row r="20">
@@ -23926,28 +23926,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>288.7338416634806</v>
+        <v>289.3746615468078</v>
       </c>
       <c r="C20" t="n">
-        <v>271.2728917710076</v>
+        <v>271.9137116543347</v>
       </c>
       <c r="D20" t="n">
-        <v>260.683041620683</v>
+        <v>261.3238615040102</v>
       </c>
       <c r="E20" t="n">
-        <v>287.9303700722618</v>
+        <v>288.571189955589</v>
       </c>
       <c r="F20" t="n">
-        <v>312.8760457417138</v>
+        <v>313.5168656250387</v>
       </c>
       <c r="G20" t="n">
-        <v>321.302737515135</v>
+        <v>321.9435573984623</v>
       </c>
       <c r="H20" t="n">
-        <v>245.4748021157671</v>
+        <v>246.1156219990944</v>
       </c>
       <c r="I20" t="n">
-        <v>116.4758895704059</v>
+        <v>117.1167094537331</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -23974,28 +23974,28 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>55.8691179411497</v>
+        <v>56.50993782447691</v>
       </c>
       <c r="S20" t="n">
-        <v>115.0200695862453</v>
+        <v>115.6608894695726</v>
       </c>
       <c r="T20" t="n">
-        <v>129.0958495641314</v>
+        <v>129.7366694474586</v>
       </c>
       <c r="U20" t="n">
-        <v>157.3456529078365</v>
+        <v>157.9864727911637</v>
       </c>
       <c r="V20" t="n">
-        <v>233.7522584701349</v>
+        <v>234.3930783534621</v>
       </c>
       <c r="W20" t="n">
-        <v>255.240968717413</v>
+        <v>255.8817886007402</v>
       </c>
       <c r="X20" t="n">
-        <v>275.731100678469</v>
+        <v>276.3719205617963</v>
       </c>
       <c r="Y20" t="n">
-        <v>292.2379386560536</v>
+        <v>292.8787585393808</v>
       </c>
     </row>
     <row r="21">
@@ -24005,25 +24005,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>72.53318364986734</v>
+        <v>73.17400353319456</v>
       </c>
       <c r="C21" t="n">
-        <v>78.70849898831574</v>
+        <v>79.34931887164296</v>
       </c>
       <c r="D21" t="n">
-        <v>53.44506556463875</v>
+        <v>54.08588544796598</v>
       </c>
       <c r="E21" t="n">
-        <v>63.64508045540094</v>
+        <v>64.28590033872817</v>
       </c>
       <c r="F21" t="n">
-        <v>51.06921239338388</v>
+        <v>51.7100322767111</v>
       </c>
       <c r="G21" t="n">
-        <v>43.34351716321063</v>
+        <v>43.98433704653786</v>
       </c>
       <c r="H21" t="n">
-        <v>18.23544423649646</v>
+        <v>18.87626411982369</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -24053,28 +24053,28 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>6.157834152643133</v>
+        <v>6.798654035970358</v>
       </c>
       <c r="S21" t="n">
-        <v>77.68317110383782</v>
+        <v>78.32399098716505</v>
       </c>
       <c r="T21" t="n">
-        <v>106.1647286948216</v>
+        <v>106.8055485781488</v>
       </c>
       <c r="U21" t="n">
-        <v>131.9413820809748</v>
+        <v>132.582201964302</v>
       </c>
       <c r="V21" t="n">
-        <v>138.8005871494253</v>
+        <v>139.4414070327525</v>
       </c>
       <c r="W21" t="n">
-        <v>157.6949831609196</v>
+        <v>158.3358030442468</v>
       </c>
       <c r="X21" t="n">
-        <v>111.7729852034775</v>
+        <v>112.4138050868047</v>
       </c>
       <c r="Y21" t="n">
-        <v>111.6826957773044</v>
+        <v>112.3235156606316</v>
       </c>
     </row>
     <row r="22">
@@ -24084,28 +24084,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>85.8319801819373</v>
+        <v>86.47280006526452</v>
       </c>
       <c r="C22" t="n">
-        <v>73.24682109862783</v>
+        <v>73.88764098195506</v>
       </c>
       <c r="D22" t="n">
-        <v>54.61547301821236</v>
+        <v>55.25629290153958</v>
       </c>
       <c r="E22" t="n">
-        <v>52.43396264656917</v>
+        <v>53.0747825298964</v>
       </c>
       <c r="F22" t="n">
-        <v>51.42104802293125</v>
+        <v>52.06186790625847</v>
       </c>
       <c r="G22" t="n">
-        <v>73.99097935845876</v>
+        <v>74.63179924178598</v>
       </c>
       <c r="H22" t="n">
-        <v>68.22717250743958</v>
+        <v>68.8679923907668</v>
       </c>
       <c r="I22" t="n">
-        <v>61.45047492725828</v>
+        <v>62.09129481058551</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -24132,28 +24132,28 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>83.29339137716948</v>
+        <v>83.93421126049671</v>
       </c>
       <c r="S22" t="n">
-        <v>130.0165980369723</v>
+        <v>130.6574179202995</v>
       </c>
       <c r="T22" t="n">
-        <v>133.9455894282815</v>
+        <v>134.5864093116087</v>
       </c>
       <c r="U22" t="n">
-        <v>192.3190293564909</v>
+        <v>192.9598492398181</v>
       </c>
       <c r="V22" t="n">
-        <v>158.137643323828</v>
+        <v>158.7784632071552</v>
       </c>
       <c r="W22" t="n">
-        <v>192.522998336591</v>
+        <v>193.1638182199182</v>
       </c>
       <c r="X22" t="n">
-        <v>131.7096553890372</v>
+        <v>132.3504752723644</v>
       </c>
       <c r="Y22" t="n">
-        <v>124.5846533520948</v>
+        <v>125.225473235422</v>
       </c>
     </row>
     <row r="23">
@@ -24163,28 +24163,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>288.7338416634806</v>
+        <v>289.3746615468078</v>
       </c>
       <c r="C23" t="n">
-        <v>271.2728917710076</v>
+        <v>271.9137116543347</v>
       </c>
       <c r="D23" t="n">
-        <v>260.683041620683</v>
+        <v>261.3238615040102</v>
       </c>
       <c r="E23" t="n">
-        <v>287.9303700722618</v>
+        <v>288.571189955589</v>
       </c>
       <c r="F23" t="n">
-        <v>312.8760457417114</v>
+        <v>313.5168656250387</v>
       </c>
       <c r="G23" t="n">
-        <v>321.302737515135</v>
+        <v>321.9435573984623</v>
       </c>
       <c r="H23" t="n">
-        <v>245.4748021157671</v>
+        <v>246.1156219990944</v>
       </c>
       <c r="I23" t="n">
-        <v>116.4758895704059</v>
+        <v>117.1167094537331</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -24211,28 +24211,28 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>55.8691179411497</v>
+        <v>56.50993782447691</v>
       </c>
       <c r="S23" t="n">
-        <v>115.0200695862453</v>
+        <v>115.6608894695726</v>
       </c>
       <c r="T23" t="n">
-        <v>129.0958495641314</v>
+        <v>129.7366694474586</v>
       </c>
       <c r="U23" t="n">
-        <v>157.3456529078365</v>
+        <v>157.9864727911637</v>
       </c>
       <c r="V23" t="n">
-        <v>233.7522584701349</v>
+        <v>234.3930783534621</v>
       </c>
       <c r="W23" t="n">
-        <v>255.240968717413</v>
+        <v>255.8817886007402</v>
       </c>
       <c r="X23" t="n">
-        <v>275.7311006784728</v>
+        <v>276.3719205617963</v>
       </c>
       <c r="Y23" t="n">
-        <v>292.2379386560536</v>
+        <v>292.8787585393808</v>
       </c>
     </row>
     <row r="24">
@@ -24242,25 +24242,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>72.53318364986734</v>
+        <v>73.17400353319456</v>
       </c>
       <c r="C24" t="n">
-        <v>78.70849898831574</v>
+        <v>79.34931887164296</v>
       </c>
       <c r="D24" t="n">
-        <v>53.44506556463875</v>
+        <v>54.08588544796598</v>
       </c>
       <c r="E24" t="n">
-        <v>63.64508045540094</v>
+        <v>64.28590033872817</v>
       </c>
       <c r="F24" t="n">
-        <v>51.06921239338388</v>
+        <v>51.7100322767111</v>
       </c>
       <c r="G24" t="n">
-        <v>43.34351716321063</v>
+        <v>43.98433704653786</v>
       </c>
       <c r="H24" t="n">
-        <v>18.23544423649646</v>
+        <v>18.87626411982369</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -24290,28 +24290,28 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>6.157834152643133</v>
+        <v>6.798654035970358</v>
       </c>
       <c r="S24" t="n">
-        <v>77.68317110383782</v>
+        <v>78.32399098716505</v>
       </c>
       <c r="T24" t="n">
-        <v>106.1647286948216</v>
+        <v>106.8055485781488</v>
       </c>
       <c r="U24" t="n">
-        <v>131.9413820809748</v>
+        <v>132.582201964302</v>
       </c>
       <c r="V24" t="n">
-        <v>138.8005871494253</v>
+        <v>139.4414070327525</v>
       </c>
       <c r="W24" t="n">
-        <v>157.6949831609196</v>
+        <v>158.3358030442468</v>
       </c>
       <c r="X24" t="n">
-        <v>111.7729852034775</v>
+        <v>112.4138050868047</v>
       </c>
       <c r="Y24" t="n">
-        <v>111.6826957773044</v>
+        <v>112.3235156606316</v>
       </c>
     </row>
     <row r="25">
@@ -24321,28 +24321,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>85.8319801819373</v>
+        <v>86.47280006526452</v>
       </c>
       <c r="C25" t="n">
-        <v>73.24682109862783</v>
+        <v>73.88764098195506</v>
       </c>
       <c r="D25" t="n">
-        <v>54.61547301821236</v>
+        <v>55.25629290153958</v>
       </c>
       <c r="E25" t="n">
-        <v>52.43396264656917</v>
+        <v>53.0747825298964</v>
       </c>
       <c r="F25" t="n">
-        <v>51.42104802293125</v>
+        <v>52.06186790625847</v>
       </c>
       <c r="G25" t="n">
-        <v>73.99097935845876</v>
+        <v>74.63179924178598</v>
       </c>
       <c r="H25" t="n">
-        <v>68.22717250743958</v>
+        <v>68.8679923907668</v>
       </c>
       <c r="I25" t="n">
-        <v>61.45047492725828</v>
+        <v>62.09129481058551</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -24369,28 +24369,28 @@
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>83.29339137716948</v>
+        <v>83.93421126049671</v>
       </c>
       <c r="S25" t="n">
-        <v>130.0165980369723</v>
+        <v>130.6574179202995</v>
       </c>
       <c r="T25" t="n">
-        <v>133.9455894282815</v>
+        <v>134.5864093116087</v>
       </c>
       <c r="U25" t="n">
-        <v>192.3190293564909</v>
+        <v>192.9598492398181</v>
       </c>
       <c r="V25" t="n">
-        <v>158.137643323828</v>
+        <v>158.7784632071552</v>
       </c>
       <c r="W25" t="n">
-        <v>192.522998336591</v>
+        <v>193.1638182199182</v>
       </c>
       <c r="X25" t="n">
-        <v>131.7096553890372</v>
+        <v>132.3504752723644</v>
       </c>
       <c r="Y25" t="n">
-        <v>124.5846533520948</v>
+        <v>125.225473235422</v>
       </c>
     </row>
     <row r="26">
@@ -24400,28 +24400,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>286.7338416634806</v>
+        <v>293.3372088120655</v>
       </c>
       <c r="C26" t="n">
-        <v>269.2728917710076</v>
+        <v>275.8762589195925</v>
       </c>
       <c r="D26" t="n">
-        <v>258.683041620683</v>
+        <v>265.2864087692679</v>
       </c>
       <c r="E26" t="n">
-        <v>285.9303700722618</v>
+        <v>292.5337372208467</v>
       </c>
       <c r="F26" t="n">
-        <v>310.8760457417114</v>
+        <v>317.4794128902964</v>
       </c>
       <c r="G26" t="n">
-        <v>319.302737515135</v>
+        <v>325.90610466372</v>
       </c>
       <c r="H26" t="n">
-        <v>243.4748021157671</v>
+        <v>250.0781692643521</v>
       </c>
       <c r="I26" t="n">
-        <v>114.4758895704059</v>
+        <v>121.0792567189908</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -24433,7 +24433,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>4.154841031397571e-13</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -24448,28 +24448,28 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>53.8691179411497</v>
+        <v>60.4724850897346</v>
       </c>
       <c r="S26" t="n">
-        <v>113.0200695862453</v>
+        <v>119.6234367348303</v>
       </c>
       <c r="T26" t="n">
-        <v>127.0958495641314</v>
+        <v>133.6992167127163</v>
       </c>
       <c r="U26" t="n">
-        <v>155.3456529078365</v>
+        <v>161.9490200564214</v>
       </c>
       <c r="V26" t="n">
-        <v>231.7522584701349</v>
+        <v>238.3556256187198</v>
       </c>
       <c r="W26" t="n">
-        <v>253.240968717413</v>
+        <v>259.8443358659979</v>
       </c>
       <c r="X26" t="n">
-        <v>273.731100678469</v>
+        <v>280.334467827054</v>
       </c>
       <c r="Y26" t="n">
-        <v>290.2379386560536</v>
+        <v>296.8413058046385</v>
       </c>
     </row>
     <row r="27">
@@ -24479,25 +24479,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>70.53318364986734</v>
+        <v>77.13655079845226</v>
       </c>
       <c r="C27" t="n">
-        <v>76.70849898831574</v>
+        <v>83.31186613690066</v>
       </c>
       <c r="D27" t="n">
-        <v>51.44506556463875</v>
+        <v>58.04843271322368</v>
       </c>
       <c r="E27" t="n">
-        <v>61.64508045540094</v>
+        <v>68.24844760398587</v>
       </c>
       <c r="F27" t="n">
-        <v>49.06921239338388</v>
+        <v>55.6725795419688</v>
       </c>
       <c r="G27" t="n">
-        <v>41.34351716321063</v>
+        <v>47.94688431179556</v>
       </c>
       <c r="H27" t="n">
-        <v>16.23544423649646</v>
+        <v>22.83881138508139</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -24527,28 +24527,28 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>4.157834152643133</v>
+        <v>10.76120130122806</v>
       </c>
       <c r="S27" t="n">
-        <v>75.68317110383782</v>
+        <v>82.28653825242274</v>
       </c>
       <c r="T27" t="n">
-        <v>104.1647286948216</v>
+        <v>110.7680958434065</v>
       </c>
       <c r="U27" t="n">
-        <v>129.9413820809748</v>
+        <v>136.5447492295597</v>
       </c>
       <c r="V27" t="n">
-        <v>136.8005871494253</v>
+        <v>143.4039542980102</v>
       </c>
       <c r="W27" t="n">
-        <v>155.6949831609196</v>
+        <v>162.2983503095045</v>
       </c>
       <c r="X27" t="n">
-        <v>109.7729852034775</v>
+        <v>116.3763523520624</v>
       </c>
       <c r="Y27" t="n">
-        <v>109.6826957773044</v>
+        <v>116.2860629258893</v>
       </c>
     </row>
     <row r="28">
@@ -24558,31 +24558,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>83.8319801819373</v>
+        <v>90.43534733052222</v>
       </c>
       <c r="C28" t="n">
-        <v>71.24682109862783</v>
+        <v>77.85018824721276</v>
       </c>
       <c r="D28" t="n">
-        <v>52.61547301821236</v>
+        <v>59.21884016679728</v>
       </c>
       <c r="E28" t="n">
-        <v>50.43396264656917</v>
+        <v>57.03732979515409</v>
       </c>
       <c r="F28" t="n">
-        <v>49.42104802293125</v>
+        <v>56.02441517151617</v>
       </c>
       <c r="G28" t="n">
-        <v>71.99097935845876</v>
+        <v>78.59434650704368</v>
       </c>
       <c r="H28" t="n">
-        <v>66.22717250743958</v>
+        <v>72.8305396560245</v>
       </c>
       <c r="I28" t="n">
-        <v>59.45047492725828</v>
+        <v>66.05384207584321</v>
       </c>
       <c r="J28" t="n">
-        <v>7.105427357601002e-15</v>
+        <v>3.962547265257697</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -24606,28 +24606,28 @@
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>81.29339137716948</v>
+        <v>87.89675852575441</v>
       </c>
       <c r="S28" t="n">
-        <v>128.0165980369723</v>
+        <v>134.6199651855572</v>
       </c>
       <c r="T28" t="n">
-        <v>131.9455894282815</v>
+        <v>138.5489565768664</v>
       </c>
       <c r="U28" t="n">
-        <v>190.3190293564909</v>
+        <v>196.9223965050758</v>
       </c>
       <c r="V28" t="n">
-        <v>156.137643323828</v>
+        <v>162.7410104724129</v>
       </c>
       <c r="W28" t="n">
-        <v>190.522998336591</v>
+        <v>197.1263654851759</v>
       </c>
       <c r="X28" t="n">
-        <v>129.7096553890372</v>
+        <v>136.3130225376221</v>
       </c>
       <c r="Y28" t="n">
-        <v>122.5846533520948</v>
+        <v>129.1880205006797</v>
       </c>
     </row>
     <row r="29">
@@ -24637,28 +24637,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>248.7338416634806</v>
+        <v>248.0083636542151</v>
       </c>
       <c r="C29" t="n">
-        <v>231.2728917710076</v>
+        <v>230.5474137617421</v>
       </c>
       <c r="D29" t="n">
-        <v>220.683041620683</v>
+        <v>219.9575636114175</v>
       </c>
       <c r="E29" t="n">
-        <v>247.9303700722618</v>
+        <v>247.2048920629963</v>
       </c>
       <c r="F29" t="n">
-        <v>272.8760457417114</v>
+        <v>272.150567732446</v>
       </c>
       <c r="G29" t="n">
-        <v>281.302737515135</v>
+        <v>280.5772595058696</v>
       </c>
       <c r="H29" t="n">
-        <v>205.4748021157671</v>
+        <v>204.7493241065017</v>
       </c>
       <c r="I29" t="n">
-        <v>76.47588957040591</v>
+        <v>75.75041156114045</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -24685,28 +24685,28 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>15.8691179411497</v>
+        <v>15.14363993188422</v>
       </c>
       <c r="S29" t="n">
-        <v>75.02006958624534</v>
+        <v>74.29459157697988</v>
       </c>
       <c r="T29" t="n">
-        <v>89.09584956413136</v>
+        <v>88.3703715548659</v>
       </c>
       <c r="U29" t="n">
-        <v>117.3456529078365</v>
+        <v>116.620174898571</v>
       </c>
       <c r="V29" t="n">
-        <v>193.7522584701349</v>
+        <v>193.0267804608694</v>
       </c>
       <c r="W29" t="n">
-        <v>215.240968717413</v>
+        <v>214.5154907081476</v>
       </c>
       <c r="X29" t="n">
-        <v>235.731100678469</v>
+        <v>235.0056226692036</v>
       </c>
       <c r="Y29" t="n">
-        <v>252.2379386560536</v>
+        <v>251.5124606467881</v>
       </c>
     </row>
     <row r="30">
@@ -24716,22 +24716,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>32.53318364986734</v>
+        <v>31.80770564060188</v>
       </c>
       <c r="C30" t="n">
-        <v>38.70849898831574</v>
+        <v>37.98302097905028</v>
       </c>
       <c r="D30" t="n">
-        <v>13.44506556463875</v>
+        <v>12.71958755537329</v>
       </c>
       <c r="E30" t="n">
-        <v>23.64508045540094</v>
+        <v>22.91960244613549</v>
       </c>
       <c r="F30" t="n">
-        <v>11.06921239338388</v>
+        <v>10.34373438411842</v>
       </c>
       <c r="G30" t="n">
-        <v>3.343517163210635</v>
+        <v>2.618039153945176</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -24767,25 +24767,25 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>37.68317110383782</v>
+        <v>36.95769309457236</v>
       </c>
       <c r="T30" t="n">
-        <v>66.1647286948216</v>
+        <v>65.43925068555615</v>
       </c>
       <c r="U30" t="n">
-        <v>91.94138208097482</v>
+        <v>91.21590407170936</v>
       </c>
       <c r="V30" t="n">
-        <v>98.80058714942527</v>
+        <v>98.07510914015981</v>
       </c>
       <c r="W30" t="n">
-        <v>117.6949831609196</v>
+        <v>116.9695051516541</v>
       </c>
       <c r="X30" t="n">
-        <v>71.77298520347748</v>
+        <v>71.04750719421202</v>
       </c>
       <c r="Y30" t="n">
-        <v>71.68269577730436</v>
+        <v>70.9572177680389</v>
       </c>
     </row>
     <row r="31">
@@ -24795,28 +24795,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>45.8319801819373</v>
+        <v>45.10650217267184</v>
       </c>
       <c r="C31" t="n">
-        <v>33.24682109862783</v>
+        <v>32.52134308936238</v>
       </c>
       <c r="D31" t="n">
-        <v>14.61547301821236</v>
+        <v>13.8899950089469</v>
       </c>
       <c r="E31" t="n">
-        <v>12.43396264656917</v>
+        <v>11.70848463730371</v>
       </c>
       <c r="F31" t="n">
-        <v>11.42104802293125</v>
+        <v>10.69557001366579</v>
       </c>
       <c r="G31" t="n">
-        <v>33.99097935845876</v>
+        <v>33.2655013491933</v>
       </c>
       <c r="H31" t="n">
-        <v>28.22717250743958</v>
+        <v>27.50169449817412</v>
       </c>
       <c r="I31" t="n">
-        <v>21.45047492725828</v>
+        <v>20.72499691799283</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -24843,28 +24843,28 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>43.29339137716948</v>
+        <v>42.56791336790403</v>
       </c>
       <c r="S31" t="n">
-        <v>90.01659803697225</v>
+        <v>89.2911200277068</v>
       </c>
       <c r="T31" t="n">
-        <v>93.94558942828149</v>
+        <v>93.22011141901604</v>
       </c>
       <c r="U31" t="n">
-        <v>152.3190293564909</v>
+        <v>151.5935513472254</v>
       </c>
       <c r="V31" t="n">
-        <v>118.137643323828</v>
+        <v>117.4121653145625</v>
       </c>
       <c r="W31" t="n">
-        <v>152.522998336591</v>
+        <v>151.7975203273255</v>
       </c>
       <c r="X31" t="n">
-        <v>91.70965538903715</v>
+        <v>90.98417737977169</v>
       </c>
       <c r="Y31" t="n">
-        <v>84.58465335209479</v>
+        <v>83.85917534282933</v>
       </c>
     </row>
     <row r="32">
@@ -24874,28 +24874,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>248.7338416634806</v>
+        <v>248.0083636542151</v>
       </c>
       <c r="C32" t="n">
-        <v>231.2728917710076</v>
+        <v>230.5474137617421</v>
       </c>
       <c r="D32" t="n">
-        <v>220.683041620683</v>
+        <v>219.9575636114175</v>
       </c>
       <c r="E32" t="n">
-        <v>247.9303700722618</v>
+        <v>247.2048920629963</v>
       </c>
       <c r="F32" t="n">
-        <v>272.8760457417114</v>
+        <v>272.150567732446</v>
       </c>
       <c r="G32" t="n">
-        <v>281.302737515135</v>
+        <v>280.5772595058696</v>
       </c>
       <c r="H32" t="n">
-        <v>205.4748021157671</v>
+        <v>204.7493241065017</v>
       </c>
       <c r="I32" t="n">
-        <v>76.47588957040591</v>
+        <v>75.75041156114045</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -24922,28 +24922,28 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>15.8691179411497</v>
+        <v>15.14363993188422</v>
       </c>
       <c r="S32" t="n">
-        <v>75.02006958624534</v>
+        <v>74.29459157697988</v>
       </c>
       <c r="T32" t="n">
-        <v>89.09584956413136</v>
+        <v>88.3703715548659</v>
       </c>
       <c r="U32" t="n">
-        <v>117.3456529078365</v>
+        <v>116.620174898571</v>
       </c>
       <c r="V32" t="n">
-        <v>193.7522584701349</v>
+        <v>193.0267804608694</v>
       </c>
       <c r="W32" t="n">
-        <v>215.240968717413</v>
+        <v>214.5154907081476</v>
       </c>
       <c r="X32" t="n">
-        <v>235.731100678469</v>
+        <v>235.0056226692036</v>
       </c>
       <c r="Y32" t="n">
-        <v>252.2379386560536</v>
+        <v>251.5124606467881</v>
       </c>
     </row>
     <row r="33">
@@ -24953,22 +24953,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>32.53318364986734</v>
+        <v>31.80770564060188</v>
       </c>
       <c r="C33" t="n">
-        <v>38.70849898831574</v>
+        <v>37.98302097905028</v>
       </c>
       <c r="D33" t="n">
-        <v>13.44506556463875</v>
+        <v>12.71958755537329</v>
       </c>
       <c r="E33" t="n">
-        <v>23.64508045540094</v>
+        <v>22.91960244613549</v>
       </c>
       <c r="F33" t="n">
-        <v>11.06921239338388</v>
+        <v>10.34373438411842</v>
       </c>
       <c r="G33" t="n">
-        <v>3.343517163210635</v>
+        <v>2.618039153945176</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -25004,25 +25004,25 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>37.68317110383782</v>
+        <v>36.95769309457236</v>
       </c>
       <c r="T33" t="n">
-        <v>66.1647286948216</v>
+        <v>65.43925068555615</v>
       </c>
       <c r="U33" t="n">
-        <v>91.94138208097482</v>
+        <v>91.21590407170936</v>
       </c>
       <c r="V33" t="n">
-        <v>98.80058714942527</v>
+        <v>98.07510914015981</v>
       </c>
       <c r="W33" t="n">
-        <v>117.6949831609196</v>
+        <v>116.9695051516541</v>
       </c>
       <c r="X33" t="n">
-        <v>71.77298520347748</v>
+        <v>71.04750719421202</v>
       </c>
       <c r="Y33" t="n">
-        <v>71.68269577730436</v>
+        <v>70.9572177680389</v>
       </c>
     </row>
     <row r="34">
@@ -25032,28 +25032,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>45.8319801819373</v>
+        <v>45.10650217267184</v>
       </c>
       <c r="C34" t="n">
-        <v>33.24682109862783</v>
+        <v>32.52134308936238</v>
       </c>
       <c r="D34" t="n">
-        <v>14.61547301821236</v>
+        <v>13.8899950089469</v>
       </c>
       <c r="E34" t="n">
-        <v>12.43396264656917</v>
+        <v>11.70848463730371</v>
       </c>
       <c r="F34" t="n">
-        <v>11.42104802293125</v>
+        <v>10.69557001366579</v>
       </c>
       <c r="G34" t="n">
-        <v>33.99097935845876</v>
+        <v>33.2655013491933</v>
       </c>
       <c r="H34" t="n">
-        <v>28.22717250743958</v>
+        <v>27.50169449817412</v>
       </c>
       <c r="I34" t="n">
-        <v>21.45047492725828</v>
+        <v>20.72499691799283</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -25080,28 +25080,28 @@
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>43.29339137716948</v>
+        <v>42.56791336790403</v>
       </c>
       <c r="S34" t="n">
-        <v>90.01659803697225</v>
+        <v>89.2911200277068</v>
       </c>
       <c r="T34" t="n">
-        <v>93.94558942828149</v>
+        <v>93.22011141901604</v>
       </c>
       <c r="U34" t="n">
-        <v>152.3190293564909</v>
+        <v>151.5935513472254</v>
       </c>
       <c r="V34" t="n">
-        <v>118.137643323828</v>
+        <v>117.4121653145625</v>
       </c>
       <c r="W34" t="n">
-        <v>152.522998336591</v>
+        <v>151.7975203273255</v>
       </c>
       <c r="X34" t="n">
-        <v>91.70965538903715</v>
+        <v>90.98417737977169</v>
       </c>
       <c r="Y34" t="n">
-        <v>84.58465335209479</v>
+        <v>83.85917534282933</v>
       </c>
     </row>
     <row r="35">
@@ -25111,28 +25111,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>248.7338416634806</v>
+        <v>248.0083636542151</v>
       </c>
       <c r="C35" t="n">
-        <v>231.2728917710076</v>
+        <v>230.5474137617421</v>
       </c>
       <c r="D35" t="n">
-        <v>220.683041620683</v>
+        <v>219.9575636114175</v>
       </c>
       <c r="E35" t="n">
-        <v>247.9303700722618</v>
+        <v>247.2048920629963</v>
       </c>
       <c r="F35" t="n">
-        <v>272.8760457417114</v>
+        <v>272.150567732446</v>
       </c>
       <c r="G35" t="n">
-        <v>281.302737515135</v>
+        <v>280.5772595058696</v>
       </c>
       <c r="H35" t="n">
-        <v>205.4748021157671</v>
+        <v>204.7493241065017</v>
       </c>
       <c r="I35" t="n">
-        <v>76.47588957040591</v>
+        <v>75.75041156114045</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -25159,28 +25159,28 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>15.8691179411497</v>
+        <v>15.14363993188422</v>
       </c>
       <c r="S35" t="n">
-        <v>75.02006958624534</v>
+        <v>74.29459157697988</v>
       </c>
       <c r="T35" t="n">
-        <v>89.09584956413136</v>
+        <v>88.3703715548659</v>
       </c>
       <c r="U35" t="n">
-        <v>117.3456529078365</v>
+        <v>116.620174898571</v>
       </c>
       <c r="V35" t="n">
-        <v>193.7522584701349</v>
+        <v>193.0267804608694</v>
       </c>
       <c r="W35" t="n">
-        <v>215.240968717413</v>
+        <v>214.5154907081476</v>
       </c>
       <c r="X35" t="n">
-        <v>235.731100678469</v>
+        <v>235.0056226692036</v>
       </c>
       <c r="Y35" t="n">
-        <v>252.2379386560536</v>
+        <v>251.5124606467881</v>
       </c>
     </row>
     <row r="36">
@@ -25190,22 +25190,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>32.53318364986734</v>
+        <v>31.80770564060188</v>
       </c>
       <c r="C36" t="n">
-        <v>38.70849898831574</v>
+        <v>37.98302097905028</v>
       </c>
       <c r="D36" t="n">
-        <v>13.44506556463875</v>
+        <v>12.71958755537329</v>
       </c>
       <c r="E36" t="n">
-        <v>23.64508045540094</v>
+        <v>22.91960244613549</v>
       </c>
       <c r="F36" t="n">
-        <v>11.06921239338388</v>
+        <v>10.34373438411842</v>
       </c>
       <c r="G36" t="n">
-        <v>3.343517163210635</v>
+        <v>2.618039153945176</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -25241,25 +25241,25 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>37.68317110383782</v>
+        <v>36.95769309457236</v>
       </c>
       <c r="T36" t="n">
-        <v>66.1647286948216</v>
+        <v>65.43925068555615</v>
       </c>
       <c r="U36" t="n">
-        <v>91.94138208097482</v>
+        <v>91.21590407170936</v>
       </c>
       <c r="V36" t="n">
-        <v>98.80058714942527</v>
+        <v>98.07510914015981</v>
       </c>
       <c r="W36" t="n">
-        <v>117.6949831609196</v>
+        <v>116.9695051516541</v>
       </c>
       <c r="X36" t="n">
-        <v>71.77298520347748</v>
+        <v>71.04750719421202</v>
       </c>
       <c r="Y36" t="n">
-        <v>71.68269577730436</v>
+        <v>70.9572177680389</v>
       </c>
     </row>
     <row r="37">
@@ -25269,28 +25269,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>45.8319801819373</v>
+        <v>45.10650217267184</v>
       </c>
       <c r="C37" t="n">
-        <v>33.24682109862783</v>
+        <v>32.52134308936238</v>
       </c>
       <c r="D37" t="n">
-        <v>14.61547301821236</v>
+        <v>13.8899950089469</v>
       </c>
       <c r="E37" t="n">
-        <v>12.43396264656917</v>
+        <v>11.70848463730371</v>
       </c>
       <c r="F37" t="n">
-        <v>11.42104802293125</v>
+        <v>10.69557001366579</v>
       </c>
       <c r="G37" t="n">
-        <v>33.99097935845876</v>
+        <v>33.2655013491933</v>
       </c>
       <c r="H37" t="n">
-        <v>28.22717250743958</v>
+        <v>27.50169449817412</v>
       </c>
       <c r="I37" t="n">
-        <v>21.45047492725828</v>
+        <v>20.72499691799283</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -25317,28 +25317,28 @@
         <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>43.29339137716948</v>
+        <v>42.56791336790403</v>
       </c>
       <c r="S37" t="n">
-        <v>90.01659803697225</v>
+        <v>89.2911200277068</v>
       </c>
       <c r="T37" t="n">
-        <v>93.94558942828149</v>
+        <v>93.22011141901604</v>
       </c>
       <c r="U37" t="n">
-        <v>152.3190293564909</v>
+        <v>151.5935513472254</v>
       </c>
       <c r="V37" t="n">
-        <v>118.137643323828</v>
+        <v>117.4121653145625</v>
       </c>
       <c r="W37" t="n">
-        <v>152.522998336591</v>
+        <v>151.7975203273255</v>
       </c>
       <c r="X37" t="n">
-        <v>91.70965538903715</v>
+        <v>90.98417737977169</v>
       </c>
       <c r="Y37" t="n">
-        <v>84.58465335209479</v>
+        <v>83.85917534282933</v>
       </c>
     </row>
     <row r="38">
@@ -25348,28 +25348,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>248.7338416634806</v>
+        <v>248.0083636542151</v>
       </c>
       <c r="C38" t="n">
-        <v>231.2728917710076</v>
+        <v>230.5474137617421</v>
       </c>
       <c r="D38" t="n">
-        <v>220.683041620683</v>
+        <v>219.9575636114175</v>
       </c>
       <c r="E38" t="n">
-        <v>247.9303700722618</v>
+        <v>247.2048920629963</v>
       </c>
       <c r="F38" t="n">
-        <v>272.8760457417114</v>
+        <v>272.150567732446</v>
       </c>
       <c r="G38" t="n">
-        <v>281.302737515135</v>
+        <v>280.5772595058696</v>
       </c>
       <c r="H38" t="n">
-        <v>205.4748021157671</v>
+        <v>204.7493241065017</v>
       </c>
       <c r="I38" t="n">
-        <v>76.47588957040591</v>
+        <v>75.75041156114045</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -25396,28 +25396,28 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>15.8691179411497</v>
+        <v>15.14363993188422</v>
       </c>
       <c r="S38" t="n">
-        <v>75.02006958624534</v>
+        <v>74.29459157697988</v>
       </c>
       <c r="T38" t="n">
-        <v>89.09584956413136</v>
+        <v>88.3703715548659</v>
       </c>
       <c r="U38" t="n">
-        <v>117.3456529078365</v>
+        <v>116.620174898571</v>
       </c>
       <c r="V38" t="n">
-        <v>193.7522584701349</v>
+        <v>193.0267804608694</v>
       </c>
       <c r="W38" t="n">
-        <v>215.240968717413</v>
+        <v>214.5154907081476</v>
       </c>
       <c r="X38" t="n">
-        <v>235.731100678469</v>
+        <v>235.0056226692036</v>
       </c>
       <c r="Y38" t="n">
-        <v>252.2379386560536</v>
+        <v>251.5124606467881</v>
       </c>
     </row>
     <row r="39">
@@ -25427,22 +25427,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>32.53318364986734</v>
+        <v>31.80770564060188</v>
       </c>
       <c r="C39" t="n">
-        <v>38.70849898831574</v>
+        <v>37.98302097905028</v>
       </c>
       <c r="D39" t="n">
-        <v>13.44506556463875</v>
+        <v>12.71958755537329</v>
       </c>
       <c r="E39" t="n">
-        <v>23.64508045540094</v>
+        <v>22.91960244613549</v>
       </c>
       <c r="F39" t="n">
-        <v>11.06921239338388</v>
+        <v>10.34373438411842</v>
       </c>
       <c r="G39" t="n">
-        <v>3.343517163210635</v>
+        <v>2.618039153945176</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -25478,25 +25478,25 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>37.68317110383782</v>
+        <v>36.95769309457236</v>
       </c>
       <c r="T39" t="n">
-        <v>66.1647286948216</v>
+        <v>65.43925068555615</v>
       </c>
       <c r="U39" t="n">
-        <v>91.94138208097482</v>
+        <v>91.21590407170936</v>
       </c>
       <c r="V39" t="n">
-        <v>98.80058714942527</v>
+        <v>98.07510914015981</v>
       </c>
       <c r="W39" t="n">
-        <v>117.6949831609196</v>
+        <v>116.9695051516541</v>
       </c>
       <c r="X39" t="n">
-        <v>71.77298520347748</v>
+        <v>71.04750719421202</v>
       </c>
       <c r="Y39" t="n">
-        <v>71.68269577730436</v>
+        <v>70.9572177680389</v>
       </c>
     </row>
     <row r="40">
@@ -25506,28 +25506,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>45.8319801819373</v>
+        <v>45.10650217267184</v>
       </c>
       <c r="C40" t="n">
-        <v>33.24682109862783</v>
+        <v>32.52134308936238</v>
       </c>
       <c r="D40" t="n">
-        <v>14.61547301821236</v>
+        <v>13.8899950089469</v>
       </c>
       <c r="E40" t="n">
-        <v>12.43396264656917</v>
+        <v>11.70848463730371</v>
       </c>
       <c r="F40" t="n">
-        <v>11.42104802293125</v>
+        <v>10.69557001366579</v>
       </c>
       <c r="G40" t="n">
-        <v>33.99097935845876</v>
+        <v>33.2655013491933</v>
       </c>
       <c r="H40" t="n">
-        <v>28.22717250743958</v>
+        <v>27.50169449817412</v>
       </c>
       <c r="I40" t="n">
-        <v>21.45047492725828</v>
+        <v>20.72499691799283</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -25554,28 +25554,28 @@
         <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>43.29339137716948</v>
+        <v>42.56791336790403</v>
       </c>
       <c r="S40" t="n">
-        <v>90.01659803697225</v>
+        <v>89.2911200277068</v>
       </c>
       <c r="T40" t="n">
-        <v>93.94558942828149</v>
+        <v>93.22011141901604</v>
       </c>
       <c r="U40" t="n">
-        <v>152.3190293564909</v>
+        <v>151.5935513472254</v>
       </c>
       <c r="V40" t="n">
-        <v>118.137643323828</v>
+        <v>117.4121653145625</v>
       </c>
       <c r="W40" t="n">
-        <v>152.522998336591</v>
+        <v>151.7975203273255</v>
       </c>
       <c r="X40" t="n">
-        <v>91.70965538903715</v>
+        <v>90.98417737977169</v>
       </c>
       <c r="Y40" t="n">
-        <v>84.58465335209479</v>
+        <v>83.85917534282933</v>
       </c>
     </row>
     <row r="41">
@@ -25585,28 +25585,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>285.7338416634806</v>
+        <v>282.5760075108374</v>
       </c>
       <c r="C41" t="n">
-        <v>268.2728917710076</v>
+        <v>265.1150576183644</v>
       </c>
       <c r="D41" t="n">
-        <v>257.683041620683</v>
+        <v>254.5252074680398</v>
       </c>
       <c r="E41" t="n">
-        <v>284.9303700722618</v>
+        <v>281.7725359196186</v>
       </c>
       <c r="F41" t="n">
-        <v>309.8760457417114</v>
+        <v>306.7182115890683</v>
       </c>
       <c r="G41" t="n">
-        <v>318.302737515135</v>
+        <v>315.1449033624919</v>
       </c>
       <c r="H41" t="n">
-        <v>242.4748021157671</v>
+        <v>239.316967963124</v>
       </c>
       <c r="I41" t="n">
-        <v>113.4758895704059</v>
+        <v>110.3180554177628</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -25633,28 +25633,28 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>52.8691179411497</v>
+        <v>49.71128378850655</v>
       </c>
       <c r="S41" t="n">
-        <v>112.0200695862453</v>
+        <v>108.8622354336022</v>
       </c>
       <c r="T41" t="n">
-        <v>126.0958495641314</v>
+        <v>122.9380154114882</v>
       </c>
       <c r="U41" t="n">
-        <v>154.3456529078365</v>
+        <v>151.1878187551933</v>
       </c>
       <c r="V41" t="n">
-        <v>230.7522584701349</v>
+        <v>227.5944243174918</v>
       </c>
       <c r="W41" t="n">
-        <v>252.240968717413</v>
+        <v>249.0831345647699</v>
       </c>
       <c r="X41" t="n">
-        <v>272.731100678469</v>
+        <v>269.5732665258259</v>
       </c>
       <c r="Y41" t="n">
-        <v>289.2379386560536</v>
+        <v>286.0801045034104</v>
       </c>
     </row>
     <row r="42">
@@ -25664,25 +25664,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>69.53318364986734</v>
+        <v>66.37534949722421</v>
       </c>
       <c r="C42" t="n">
-        <v>75.70849898831574</v>
+        <v>72.55066483567261</v>
       </c>
       <c r="D42" t="n">
-        <v>50.44506556463875</v>
+        <v>47.28723141199562</v>
       </c>
       <c r="E42" t="n">
-        <v>60.64508045540094</v>
+        <v>57.48724630275781</v>
       </c>
       <c r="F42" t="n">
-        <v>48.06921239338388</v>
+        <v>44.91137824074075</v>
       </c>
       <c r="G42" t="n">
-        <v>40.34351716321063</v>
+        <v>37.1856830105675</v>
       </c>
       <c r="H42" t="n">
-        <v>15.23544423649646</v>
+        <v>12.07761008385333</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -25712,28 +25712,28 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>3.157834152643133</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>74.68317110383782</v>
+        <v>71.52533695119469</v>
       </c>
       <c r="T42" t="n">
-        <v>103.1647286948216</v>
+        <v>100.0068945421785</v>
       </c>
       <c r="U42" t="n">
-        <v>128.9413820809748</v>
+        <v>125.7835479283317</v>
       </c>
       <c r="V42" t="n">
-        <v>135.8005871494253</v>
+        <v>132.6427529967821</v>
       </c>
       <c r="W42" t="n">
-        <v>154.6949831609196</v>
+        <v>151.5371490082765</v>
       </c>
       <c r="X42" t="n">
-        <v>108.7729852034775</v>
+        <v>105.6151510508343</v>
       </c>
       <c r="Y42" t="n">
-        <v>108.6826957773044</v>
+        <v>105.5248616246612</v>
       </c>
     </row>
     <row r="43">
@@ -25743,28 +25743,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>82.8319801819373</v>
+        <v>79.67414602929416</v>
       </c>
       <c r="C43" t="n">
-        <v>70.24682109862783</v>
+        <v>67.0889869459847</v>
       </c>
       <c r="D43" t="n">
-        <v>51.61547301821236</v>
+        <v>48.45763886556922</v>
       </c>
       <c r="E43" t="n">
-        <v>49.43396264656917</v>
+        <v>46.27612849392604</v>
       </c>
       <c r="F43" t="n">
-        <v>48.42104802293125</v>
+        <v>45.26321387028811</v>
       </c>
       <c r="G43" t="n">
-        <v>70.99097935845876</v>
+        <v>67.83314520581563</v>
       </c>
       <c r="H43" t="n">
-        <v>65.22717250743958</v>
+        <v>62.06933835479644</v>
       </c>
       <c r="I43" t="n">
-        <v>58.45047492725828</v>
+        <v>55.29264077461515</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -25791,28 +25791,28 @@
         <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>80.29339137716948</v>
+        <v>77.13555722452635</v>
       </c>
       <c r="S43" t="n">
-        <v>127.0165980369723</v>
+        <v>123.8587638843291</v>
       </c>
       <c r="T43" t="n">
-        <v>130.9455894282815</v>
+        <v>127.7877552756384</v>
       </c>
       <c r="U43" t="n">
-        <v>189.3190293564909</v>
+        <v>186.1611952038477</v>
       </c>
       <c r="V43" t="n">
-        <v>155.137643323828</v>
+        <v>151.9798091711849</v>
       </c>
       <c r="W43" t="n">
-        <v>189.522998336591</v>
+        <v>186.3651641839479</v>
       </c>
       <c r="X43" t="n">
-        <v>128.7096553890372</v>
+        <v>125.551821236394</v>
       </c>
       <c r="Y43" t="n">
-        <v>121.5846533520948</v>
+        <v>118.4268191994517</v>
       </c>
     </row>
     <row r="44">
@@ -26078,7 +26078,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>650787.7662506661</v>
+        <v>650787.7662506662</v>
       </c>
     </row>
     <row r="3">
@@ -26086,7 +26086,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>650787.7662506661</v>
+        <v>650787.7662506662</v>
       </c>
     </row>
     <row r="4">
@@ -26094,7 +26094,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>650787.766250666</v>
+        <v>650787.7662506662</v>
       </c>
     </row>
     <row r="5">
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>313799.3828889428</v>
+        <v>319269.7670514081</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>404966.6451748743</v>
+        <v>404011.2852600148</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>404966.6451748742</v>
+        <v>404011.2852600148</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>404966.6451748742</v>
+        <v>404011.2852600148</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>404966.6451748742</v>
+        <v>404011.2852600148</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>407948.3251748744</v>
+        <v>398041.9455577398</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>463067.7239272791</v>
+        <v>464109.3072147417</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>463067.7239272791</v>
+        <v>464109.3072147417</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>463067.7239272791</v>
+        <v>464109.3072147417</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>463067.7239272791</v>
+        <v>464109.3072147417</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>409439.1651748745</v>
+        <v>414146.9906430007</v>
       </c>
     </row>
     <row r="16">
@@ -26261,46 +26261,46 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>901203.9725887424</v>
+        <v>901203.9725887425</v>
       </c>
       <c r="C2" t="n">
-        <v>901203.9725887424</v>
+        <v>901203.9725887422</v>
       </c>
       <c r="D2" t="n">
-        <v>901203.9725887424</v>
+        <v>901203.9725887423</v>
       </c>
       <c r="E2" t="n">
-        <v>330915.9392073643</v>
+        <v>340173.5124053822</v>
       </c>
       <c r="F2" t="n">
-        <v>485198.9984604792</v>
+        <v>483582.2355276398</v>
       </c>
       <c r="G2" t="n">
-        <v>485198.9984604793</v>
+        <v>483582.2355276398</v>
       </c>
       <c r="H2" t="n">
-        <v>485198.9984604792</v>
+        <v>483582.2355276397</v>
       </c>
       <c r="I2" t="n">
-        <v>485198.9984604792</v>
+        <v>483582.2355276399</v>
       </c>
       <c r="J2" t="n">
-        <v>490244.9184604792</v>
+        <v>473480.2760314824</v>
       </c>
       <c r="K2" t="n">
-        <v>583523.9009645487</v>
+        <v>585286.5803741012</v>
       </c>
       <c r="L2" t="n">
-        <v>583523.9009645488</v>
+        <v>585286.5803741013</v>
       </c>
       <c r="M2" t="n">
-        <v>583523.9009645487</v>
+        <v>585286.5803741013</v>
       </c>
       <c r="N2" t="n">
-        <v>583523.9009645487</v>
+        <v>585286.5803741013</v>
       </c>
       <c r="O2" t="n">
-        <v>492767.8784604793</v>
+        <v>500734.9677142319</v>
       </c>
       <c r="P2" t="n">
         <v>236516.2921691821</v>
@@ -26322,10 +26322,10 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>28000</v>
+        <v>30824.15289750402</v>
       </c>
       <c r="F3" t="n">
-        <v>47200</v>
+        <v>43863.1911958342</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -26337,10 +26337,10 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>29600</v>
+        <v>27654.11508529786</v>
       </c>
       <c r="K3" t="n">
-        <v>77600</v>
+        <v>80126.26732211451</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>463150.7311021098</v>
+        <v>463844.3331297129</v>
       </c>
       <c r="C4" t="n">
-        <v>463150.7311021099</v>
+        <v>463844.333129713</v>
       </c>
       <c r="D4" t="n">
-        <v>463150.7311021098</v>
+        <v>463844.3331297129</v>
       </c>
       <c r="E4" t="n">
-        <v>167240.1556070018</v>
+        <v>172737.3194355969</v>
       </c>
       <c r="F4" t="n">
-        <v>247294.4197339226</v>
+        <v>247149.1171696497</v>
       </c>
       <c r="G4" t="n">
-        <v>247294.4197339226</v>
+        <v>247149.1171696497</v>
       </c>
       <c r="H4" t="n">
-        <v>247294.4197339226</v>
+        <v>247149.1171696497</v>
       </c>
       <c r="I4" t="n">
-        <v>247294.4197339225</v>
+        <v>247149.1171696497</v>
       </c>
       <c r="J4" t="n">
-        <v>249912.6424629691</v>
+        <v>241907.4209158952</v>
       </c>
       <c r="K4" t="n">
-        <v>298313.1625137175</v>
+        <v>299921.3821520063</v>
       </c>
       <c r="L4" t="n">
-        <v>298313.1625137175</v>
+        <v>299921.3821520064</v>
       </c>
       <c r="M4" t="n">
-        <v>298313.1625137175</v>
+        <v>299921.3821520063</v>
       </c>
       <c r="N4" t="n">
-        <v>298313.1625137175</v>
+        <v>299921.3821520064</v>
       </c>
       <c r="O4" t="n">
-        <v>251221.7538274922</v>
+        <v>256049.3124315999</v>
       </c>
       <c r="P4" t="n">
-        <v>118258.146084591</v>
+        <v>118951.7481121942</v>
       </c>
     </row>
     <row r="5">
@@ -26426,37 +26426,37 @@
         <v>33627.6</v>
       </c>
       <c r="E5" t="n">
-        <v>2942.415</v>
+        <v>3239.194637425332</v>
       </c>
       <c r="F5" t="n">
-        <v>7902.486</v>
+        <v>7848.612913228564</v>
       </c>
       <c r="G5" t="n">
-        <v>7902.486</v>
+        <v>7848.612913228564</v>
       </c>
       <c r="H5" t="n">
-        <v>7902.486</v>
+        <v>7848.612913228564</v>
       </c>
       <c r="I5" t="n">
-        <v>7902.486</v>
+        <v>7848.612913228564</v>
       </c>
       <c r="J5" t="n">
-        <v>8070.624</v>
+        <v>7515.485527185614</v>
       </c>
       <c r="K5" t="n">
-        <v>11265.246</v>
+        <v>11326.23621076094</v>
       </c>
       <c r="L5" t="n">
-        <v>11265.246</v>
+        <v>11326.23621076094</v>
       </c>
       <c r="M5" t="n">
-        <v>11265.246</v>
+        <v>11326.23621076094</v>
       </c>
       <c r="N5" t="n">
-        <v>11265.246</v>
+        <v>11326.23621076094</v>
       </c>
       <c r="O5" t="n">
-        <v>8154.693</v>
+        <v>8420.168959378556</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>404425.6414866326</v>
+        <v>403732.0394590296</v>
       </c>
       <c r="C6" t="n">
-        <v>404425.6414866325</v>
+        <v>403732.0394590292</v>
       </c>
       <c r="D6" t="n">
-        <v>404425.6414866326</v>
+        <v>403732.0394590294</v>
       </c>
       <c r="E6" t="n">
-        <v>132733.3686003625</v>
+        <v>133372.8454348559</v>
       </c>
       <c r="F6" t="n">
-        <v>182802.0927265566</v>
+        <v>184721.3142489273</v>
       </c>
       <c r="G6" t="n">
-        <v>230002.0927265567</v>
+        <v>228584.5054447615</v>
       </c>
       <c r="H6" t="n">
-        <v>230002.0927265566</v>
+        <v>228584.5054447615</v>
       </c>
       <c r="I6" t="n">
-        <v>230002.0927265567</v>
+        <v>228584.5054447616</v>
       </c>
       <c r="J6" t="n">
-        <v>202661.6519975102</v>
+        <v>196403.2545031038</v>
       </c>
       <c r="K6" t="n">
-        <v>196345.4924508311</v>
+        <v>193912.6946892194</v>
       </c>
       <c r="L6" t="n">
-        <v>273945.4924508313</v>
+        <v>274038.962011334</v>
       </c>
       <c r="M6" t="n">
-        <v>273945.4924508312</v>
+        <v>274038.962011334</v>
       </c>
       <c r="N6" t="n">
-        <v>273945.4924508312</v>
+        <v>274038.962011334</v>
       </c>
       <c r="O6" t="n">
-        <v>233391.4316329871</v>
+        <v>236265.4863232535</v>
       </c>
       <c r="P6" t="n">
-        <v>118258.1460845911</v>
+        <v>117564.5440569879</v>
       </c>
     </row>
   </sheetData>
@@ -26632,37 +26632,37 @@
         <v>400</v>
       </c>
       <c r="E2" t="n">
-        <v>35</v>
+        <v>38.53019112188002</v>
       </c>
       <c r="F2" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G2" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H2" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I2" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J2" t="n">
-        <v>96</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="K2" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="L2" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="M2" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="N2" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="O2" t="n">
-        <v>97</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -26849,10 +26849,10 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>35</v>
+        <v>38.53019112188002</v>
       </c>
       <c r="F2" t="n">
-        <v>59</v>
+        <v>54.82898899479275</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -26864,16 +26864,16 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>37</v>
+        <v>34.56764385662233</v>
       </c>
       <c r="K2" t="n">
-        <v>97</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -26944,49 +26944,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27081,10 +27081,10 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>35</v>
+        <v>38.53019112188002</v>
       </c>
       <c r="K2" t="n">
-        <v>59</v>
+        <v>54.82898899479275</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -27096,10 +27096,10 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>37</v>
+        <v>34.56764385662233</v>
       </c>
       <c r="P2" t="n">
-        <v>97</v>
+        <v>100.1578341526431</v>
       </c>
     </row>
     <row r="3">
@@ -27313,10 +27313,10 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F2" t="n">
-        <v>400.0000000000002</v>
+        <v>400</v>
       </c>
       <c r="G2" t="n">
-        <v>400.0000000000002</v>
+        <v>400</v>
       </c>
       <c r="H2" t="n">
         <v>339.4748021157671</v>
@@ -27404,7 +27404,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J3" t="n">
-        <v>0.746591326263247</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -27504,7 +27504,7 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q4" t="n">
-        <v>86.16204325168574</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R4" t="n">
         <v>177.2933913771695</v>
@@ -27550,10 +27550,10 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F5" t="n">
-        <v>400.0000000000001</v>
+        <v>400</v>
       </c>
       <c r="G5" t="n">
-        <v>400.0000000000001</v>
+        <v>400</v>
       </c>
       <c r="H5" t="n">
         <v>339.4748021157671</v>
@@ -27641,7 +27641,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J6" t="n">
-        <v>0.746591326265743</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -27714,7 +27714,7 @@
         <v>167.9909793584588</v>
       </c>
       <c r="H7" t="n">
-        <v>162.2271725074309</v>
+        <v>162.2271725074396</v>
       </c>
       <c r="I7" t="n">
         <v>155.4504749272583</v>
@@ -27787,10 +27787,10 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F8" t="n">
-        <v>400.0000000000001</v>
+        <v>400</v>
       </c>
       <c r="G8" t="n">
-        <v>400.0000000000001</v>
+        <v>400</v>
       </c>
       <c r="H8" t="n">
         <v>339.4748021157671</v>
@@ -27878,7 +27878,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J9" t="n">
-        <v>0.746591326265743</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -28012,28 +28012,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>35</v>
+        <v>38.53019112188002</v>
       </c>
       <c r="C11" t="n">
-        <v>35</v>
+        <v>38.53019112188002</v>
       </c>
       <c r="D11" t="n">
-        <v>35</v>
+        <v>38.53019112188002</v>
       </c>
       <c r="E11" t="n">
-        <v>35</v>
+        <v>38.53019112188002</v>
       </c>
       <c r="F11" t="n">
-        <v>35</v>
+        <v>38.53019112188002</v>
       </c>
       <c r="G11" t="n">
-        <v>35</v>
+        <v>38.53019112188002</v>
       </c>
       <c r="H11" t="n">
-        <v>35</v>
+        <v>38.53019112188002</v>
       </c>
       <c r="I11" t="n">
-        <v>35</v>
+        <v>38.53019112188002</v>
       </c>
       <c r="J11" t="n">
         <v>11.94928935461252</v>
@@ -28060,28 +28060,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R11" t="n">
-        <v>35</v>
+        <v>38.53019112188002</v>
       </c>
       <c r="S11" t="n">
-        <v>35</v>
+        <v>38.53019112188002</v>
       </c>
       <c r="T11" t="n">
-        <v>35</v>
+        <v>38.53019112188002</v>
       </c>
       <c r="U11" t="n">
-        <v>35</v>
+        <v>38.53019112188002</v>
       </c>
       <c r="V11" t="n">
-        <v>35</v>
+        <v>38.53019112188002</v>
       </c>
       <c r="W11" t="n">
-        <v>35</v>
+        <v>38.53019112188002</v>
       </c>
       <c r="X11" t="n">
-        <v>35</v>
+        <v>38.53019112188002</v>
       </c>
       <c r="Y11" t="n">
-        <v>35</v>
+        <v>38.53019112188002</v>
       </c>
     </row>
     <row r="12">
@@ -28091,28 +28091,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>35</v>
+        <v>38.53019112188002</v>
       </c>
       <c r="C12" t="n">
-        <v>35</v>
+        <v>38.53019112188002</v>
       </c>
       <c r="D12" t="n">
-        <v>35</v>
+        <v>38.53019112188002</v>
       </c>
       <c r="E12" t="n">
-        <v>35</v>
+        <v>38.53019112188002</v>
       </c>
       <c r="F12" t="n">
-        <v>35</v>
+        <v>38.53019112188002</v>
       </c>
       <c r="G12" t="n">
-        <v>35</v>
+        <v>38.53019112188002</v>
       </c>
       <c r="H12" t="n">
-        <v>35</v>
+        <v>38.53019112188002</v>
       </c>
       <c r="I12" t="n">
-        <v>35</v>
+        <v>38.53019112188002</v>
       </c>
       <c r="J12" t="n">
         <v>0.7465913262578567</v>
@@ -28139,28 +28139,28 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>35</v>
+        <v>38.53019112188002</v>
       </c>
       <c r="S12" t="n">
-        <v>35</v>
+        <v>38.53019112188002</v>
       </c>
       <c r="T12" t="n">
-        <v>35</v>
+        <v>38.53019112188002</v>
       </c>
       <c r="U12" t="n">
-        <v>35</v>
+        <v>38.53019112188002</v>
       </c>
       <c r="V12" t="n">
-        <v>35</v>
+        <v>38.53019112188002</v>
       </c>
       <c r="W12" t="n">
-        <v>35</v>
+        <v>38.53019112188002</v>
       </c>
       <c r="X12" t="n">
-        <v>35</v>
+        <v>38.53019112188002</v>
       </c>
       <c r="Y12" t="n">
-        <v>35</v>
+        <v>38.53019112188002</v>
       </c>
     </row>
     <row r="13">
@@ -28170,31 +28170,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>35</v>
+        <v>38.53019112188002</v>
       </c>
       <c r="C13" t="n">
-        <v>35</v>
+        <v>38.53019112188002</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>38.53019112188002</v>
       </c>
       <c r="E13" t="n">
-        <v>35</v>
+        <v>38.53019112188002</v>
       </c>
       <c r="F13" t="n">
-        <v>35</v>
+        <v>38.53019112188002</v>
       </c>
       <c r="G13" t="n">
-        <v>35</v>
+        <v>38.53019112188002</v>
       </c>
       <c r="H13" t="n">
-        <v>35</v>
+        <v>38.53019112188002</v>
       </c>
       <c r="I13" t="n">
-        <v>35</v>
+        <v>38.53019112188002</v>
       </c>
       <c r="J13" t="n">
-        <v>35</v>
+        <v>38.53019112188002</v>
       </c>
       <c r="K13" t="n">
         <v>22.26949182588285</v>
@@ -28215,31 +28215,31 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q13" t="n">
-        <v>35</v>
+        <v>38.53019112188002</v>
       </c>
       <c r="R13" t="n">
-        <v>35</v>
+        <v>38.53019112188002</v>
       </c>
       <c r="S13" t="n">
-        <v>35</v>
+        <v>38.53019112188002</v>
       </c>
       <c r="T13" t="n">
-        <v>35</v>
+        <v>38.53019112188002</v>
       </c>
       <c r="U13" t="n">
-        <v>35</v>
+        <v>38.53019112188002</v>
       </c>
       <c r="V13" t="n">
-        <v>35</v>
+        <v>38.53019112188002</v>
       </c>
       <c r="W13" t="n">
-        <v>35</v>
+        <v>38.53019112188002</v>
       </c>
       <c r="X13" t="n">
-        <v>35</v>
+        <v>38.53019112188002</v>
       </c>
       <c r="Y13" t="n">
-        <v>35</v>
+        <v>38.53019112188002</v>
       </c>
     </row>
     <row r="14">
@@ -28249,28 +28249,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>93.99999999999834</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J14" t="n">
         <v>11.94928935461252</v>
@@ -28297,28 +28297,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="15">
@@ -28328,25 +28328,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I15" t="n">
         <v>89.39663285141508</v>
@@ -28376,28 +28376,28 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="16">
@@ -28407,28 +28407,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J16" t="n">
         <v>93.35918011667277</v>
@@ -28452,31 +28452,31 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q16" t="n">
-        <v>86.16204325169446</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="17">
@@ -28486,28 +28486,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>93.99999999999784</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J17" t="n">
         <v>11.94928935461252</v>
@@ -28534,28 +28534,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="18">
@@ -28565,25 +28565,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I18" t="n">
         <v>89.39663285141508</v>
@@ -28613,28 +28613,28 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="19">
@@ -28644,28 +28644,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J19" t="n">
         <v>93.35918011667277</v>
@@ -28689,31 +28689,31 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q19" t="n">
-        <v>86.16204325169456</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="20">
@@ -28723,28 +28723,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F20" t="n">
-        <v>93.99999999999758</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J20" t="n">
         <v>11.94928935461252</v>
@@ -28771,28 +28771,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="21">
@@ -28802,25 +28802,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I21" t="n">
         <v>89.39663285141508</v>
@@ -28850,28 +28850,28 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="22">
@@ -28881,28 +28881,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J22" t="n">
         <v>93.35918011667277</v>
@@ -28929,28 +28929,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="23">
@@ -28960,28 +28960,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J23" t="n">
         <v>11.94928935461252</v>
@@ -29008,28 +29008,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X23" t="n">
-        <v>93.99999999999626</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="24">
@@ -29039,25 +29039,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I24" t="n">
         <v>89.39663285141508</v>
@@ -29087,28 +29087,28 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="25">
@@ -29118,28 +29118,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J25" t="n">
         <v>93.35918011667277</v>
@@ -29166,28 +29166,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="26">
@@ -29197,28 +29197,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>96</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="C26" t="n">
-        <v>96</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="D26" t="n">
-        <v>96</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="E26" t="n">
-        <v>96</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="F26" t="n">
-        <v>96</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="G26" t="n">
-        <v>96</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="H26" t="n">
-        <v>96</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="I26" t="n">
-        <v>96</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J26" t="n">
         <v>11.94928935461252</v>
@@ -29245,28 +29245,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R26" t="n">
-        <v>96</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="S26" t="n">
-        <v>96</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="T26" t="n">
-        <v>96</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="U26" t="n">
-        <v>96</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="V26" t="n">
-        <v>96</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="W26" t="n">
-        <v>96</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="X26" t="n">
-        <v>96</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="Y26" t="n">
-        <v>96</v>
+        <v>89.39663285141508</v>
       </c>
     </row>
     <row r="27">
@@ -29276,25 +29276,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>96</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="C27" t="n">
-        <v>96</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="D27" t="n">
-        <v>96</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="E27" t="n">
-        <v>96</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="F27" t="n">
-        <v>96</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="G27" t="n">
-        <v>96</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="H27" t="n">
-        <v>96</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="I27" t="n">
         <v>89.39663285141508</v>
@@ -29324,28 +29324,28 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>96</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="S27" t="n">
-        <v>96</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="T27" t="n">
-        <v>96</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="U27" t="n">
-        <v>96</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="V27" t="n">
-        <v>96</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="W27" t="n">
-        <v>96</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="X27" t="n">
-        <v>96</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="Y27" t="n">
-        <v>96</v>
+        <v>89.39663285141508</v>
       </c>
     </row>
     <row r="28">
@@ -29355,31 +29355,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>96</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="C28" t="n">
-        <v>96</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="D28" t="n">
-        <v>96</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="E28" t="n">
-        <v>96</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="F28" t="n">
-        <v>96</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="G28" t="n">
-        <v>96</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="H28" t="n">
-        <v>96</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="I28" t="n">
-        <v>96</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J28" t="n">
-        <v>93.35918011667277</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="K28" t="n">
         <v>22.26949182588285</v>
@@ -29403,28 +29403,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R28" t="n">
-        <v>96</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="S28" t="n">
-        <v>96</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="T28" t="n">
-        <v>96</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="U28" t="n">
-        <v>96</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="V28" t="n">
-        <v>96</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="W28" t="n">
-        <v>96</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="X28" t="n">
-        <v>96</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="Y28" t="n">
-        <v>96</v>
+        <v>89.39663285141508</v>
       </c>
     </row>
     <row r="29">
@@ -29434,28 +29434,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="C29" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="D29" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="E29" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="F29" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="G29" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="H29" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="I29" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="J29" t="n">
         <v>11.94928935461252</v>
@@ -29482,28 +29482,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R29" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="S29" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="T29" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="U29" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="V29" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="W29" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="X29" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="Y29" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
     </row>
     <row r="30">
@@ -29513,25 +29513,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="C30" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="D30" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="E30" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="F30" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="G30" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="H30" t="n">
-        <v>112.2354442364968</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I30" t="n">
         <v>89.39663285141508</v>
@@ -29564,25 +29564,25 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S30" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="T30" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="U30" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="V30" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="W30" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="X30" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="Y30" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
     </row>
     <row r="31">
@@ -29592,28 +29592,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="C31" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="D31" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="E31" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="F31" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="G31" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="H31" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="I31" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="J31" t="n">
         <v>93.35918011667277</v>
@@ -29640,28 +29640,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R31" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="S31" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="T31" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="U31" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="V31" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="W31" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="X31" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="Y31" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
     </row>
     <row r="32">
@@ -29671,28 +29671,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="C32" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="D32" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="E32" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="F32" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="G32" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="H32" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="I32" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="J32" t="n">
         <v>11.94928935461252</v>
@@ -29719,28 +29719,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R32" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="S32" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="T32" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="U32" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="V32" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="W32" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="X32" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="Y32" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
     </row>
     <row r="33">
@@ -29750,25 +29750,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="C33" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="D33" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="E33" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="F33" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="G33" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="H33" t="n">
-        <v>112.2354442364967</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I33" t="n">
         <v>89.39663285141508</v>
@@ -29798,28 +29798,28 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>100.1578341526434</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S33" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="T33" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="U33" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="V33" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="W33" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="X33" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="Y33" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
     </row>
     <row r="34">
@@ -29829,28 +29829,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="C34" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="D34" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="E34" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="F34" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="G34" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="H34" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="I34" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="J34" t="n">
         <v>93.35918011667277</v>
@@ -29877,28 +29877,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R34" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="S34" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="T34" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="U34" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="V34" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="W34" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="X34" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="Y34" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
     </row>
     <row r="35">
@@ -29908,28 +29908,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="C35" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="D35" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="E35" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="F35" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="G35" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="H35" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="I35" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="J35" t="n">
         <v>11.94928935461252</v>
@@ -29956,28 +29956,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R35" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="S35" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="T35" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="U35" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="V35" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="W35" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="X35" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="Y35" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
     </row>
     <row r="36">
@@ -29987,25 +29987,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="C36" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="D36" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="E36" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="F36" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="G36" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="H36" t="n">
-        <v>112.2354442364968</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I36" t="n">
         <v>89.39663285141508</v>
@@ -30038,25 +30038,25 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S36" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="T36" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="U36" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="V36" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="W36" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="X36" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="Y36" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
     </row>
     <row r="37">
@@ -30066,28 +30066,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="C37" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="D37" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="E37" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="F37" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="G37" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="H37" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="I37" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="J37" t="n">
         <v>93.35918011667277</v>
@@ -30114,28 +30114,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R37" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="S37" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="T37" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="U37" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="V37" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="W37" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="X37" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="Y37" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
     </row>
     <row r="38">
@@ -30145,28 +30145,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="C38" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="D38" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="E38" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="F38" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="G38" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="H38" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="I38" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="J38" t="n">
         <v>11.94928935461252</v>
@@ -30193,28 +30193,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R38" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="S38" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="T38" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="U38" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="V38" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="W38" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="X38" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="Y38" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
     </row>
     <row r="39">
@@ -30224,25 +30224,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="C39" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="D39" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="E39" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="F39" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="G39" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="H39" t="n">
-        <v>112.2354442364968</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I39" t="n">
         <v>89.39663285141508</v>
@@ -30275,25 +30275,25 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S39" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="T39" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="U39" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="V39" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="W39" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="X39" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="Y39" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
     </row>
     <row r="40">
@@ -30303,28 +30303,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="C40" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="D40" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="E40" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="F40" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="G40" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="H40" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="I40" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="J40" t="n">
         <v>93.35918011667277</v>
@@ -30351,28 +30351,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R40" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="S40" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="T40" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="U40" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="V40" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="W40" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="X40" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
       <c r="Y40" t="n">
-        <v>134</v>
+        <v>134.7254780092655</v>
       </c>
     </row>
     <row r="41">
@@ -30382,28 +30382,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>97</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="C41" t="n">
-        <v>97</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="D41" t="n">
-        <v>97</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="E41" t="n">
-        <v>97</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="F41" t="n">
-        <v>97</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="G41" t="n">
-        <v>97</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="H41" t="n">
-        <v>97</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="I41" t="n">
-        <v>97</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="J41" t="n">
         <v>11.94928935461252</v>
@@ -30430,28 +30430,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R41" t="n">
-        <v>97</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S41" t="n">
-        <v>97</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="T41" t="n">
-        <v>97</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="U41" t="n">
-        <v>97</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="V41" t="n">
-        <v>97</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="W41" t="n">
-        <v>97</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="X41" t="n">
-        <v>97</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="Y41" t="n">
-        <v>97</v>
+        <v>100.1578341526431</v>
       </c>
     </row>
     <row r="42">
@@ -30461,25 +30461,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>97</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="C42" t="n">
-        <v>97</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="D42" t="n">
-        <v>97</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="E42" t="n">
-        <v>97</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="F42" t="n">
-        <v>97</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="G42" t="n">
-        <v>97</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="H42" t="n">
-        <v>97</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="I42" t="n">
         <v>89.39663285141508</v>
@@ -30509,28 +30509,28 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>97</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S42" t="n">
-        <v>97</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="T42" t="n">
-        <v>97</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="U42" t="n">
-        <v>97</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="V42" t="n">
-        <v>97</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="W42" t="n">
-        <v>97</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="X42" t="n">
-        <v>97</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="Y42" t="n">
-        <v>97</v>
+        <v>100.1578341526431</v>
       </c>
     </row>
     <row r="43">
@@ -30540,28 +30540,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>97</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="C43" t="n">
-        <v>97</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="D43" t="n">
-        <v>97</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="E43" t="n">
-        <v>97</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="F43" t="n">
-        <v>97</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="G43" t="n">
-        <v>97</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="H43" t="n">
-        <v>97</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="I43" t="n">
-        <v>97</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="J43" t="n">
         <v>93.35918011667277</v>
@@ -30588,28 +30588,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R43" t="n">
-        <v>97</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S43" t="n">
-        <v>97</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="T43" t="n">
-        <v>97</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="U43" t="n">
-        <v>97</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="V43" t="n">
-        <v>97</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="W43" t="n">
-        <v>97</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="X43" t="n">
-        <v>97</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="Y43" t="n">
-        <v>97</v>
+        <v>100.1578341526431</v>
       </c>
     </row>
     <row r="44">
